--- a/districtuser.xlsx
+++ b/districtuser.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\laragon\www\bonfe\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{088D1D81-CB39-46A4-B77F-7A451423FE36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB919E56-3216-4A43-A26C-B8F3418984B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="3060" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="521" uniqueCount="250">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="586" uniqueCount="252">
   <si>
     <t>Gender</t>
   </si>
@@ -775,6 +775,12 @@
   </si>
   <si>
     <t>last_name</t>
+  </si>
+  <si>
+    <t>Password</t>
+  </si>
+  <si>
+    <t>password</t>
   </si>
 </sst>
 </file>
@@ -902,7 +908,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -930,7 +936,6 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -944,6 +949,8 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1259,7 +1266,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K257"/>
+  <dimension ref="A1:L257"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="22" style="5" customWidth="1"/>
@@ -1272,9 +1279,10 @@
     <col min="8" max="8" width="14.21875" style="5" customWidth="1"/>
     <col min="9" max="9" width="11" style="5" customWidth="1"/>
     <col min="10" max="11" width="9.109375" style="5"/>
+    <col min="12" max="12" width="10.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" s="11" t="s">
         <v>248</v>
       </c>
@@ -1293,7 +1301,7 @@
       <c r="F1" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="G1" s="18" t="s">
+      <c r="G1" s="17" t="s">
         <v>8</v>
       </c>
       <c r="H1" s="11" t="s">
@@ -1308,8 +1316,11 @@
       <c r="K1" s="12" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:11" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+      <c r="L1" s="18" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>140</v>
       </c>
@@ -1328,7 +1339,7 @@
       <c r="F2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="G2" s="14" t="s">
+      <c r="G2" s="13" t="s">
         <v>7</v>
       </c>
       <c r="H2" s="4">
@@ -1339,8 +1350,11 @@
       </c>
       <c r="J2" s="2"/>
       <c r="K2" s="2"/>
-    </row>
-    <row r="3" spans="1:11" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+      <c r="L2" s="19" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
         <v>159</v>
       </c>
@@ -1359,7 +1373,7 @@
       <c r="F3" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="G3" s="14" t="s">
+      <c r="G3" s="13" t="s">
         <v>15</v>
       </c>
       <c r="H3" s="7">
@@ -1370,8 +1384,11 @@
       </c>
       <c r="J3" s="2"/>
       <c r="K3" s="2"/>
-    </row>
-    <row r="4" spans="1:11" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+      <c r="L3" s="19" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
         <v>142</v>
       </c>
@@ -1390,7 +1407,7 @@
       <c r="F4" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="G4" s="14" t="s">
+      <c r="G4" s="13" t="s">
         <v>16</v>
       </c>
       <c r="H4" s="7">
@@ -1401,8 +1418,11 @@
       </c>
       <c r="J4" s="2"/>
       <c r="K4" s="2"/>
-    </row>
-    <row r="5" spans="1:11" s="1" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L4" s="19" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" s="1" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
         <v>161</v>
       </c>
@@ -1421,7 +1441,7 @@
       <c r="F5" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="G5" s="16" t="s">
+      <c r="G5" s="15" t="s">
         <v>17</v>
       </c>
       <c r="H5" s="7">
@@ -1432,8 +1452,11 @@
       </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
-    </row>
-    <row r="6" spans="1:11" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+      <c r="L5" s="19" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>247</v>
       </c>
@@ -1452,7 +1475,7 @@
       <c r="F6" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="G6" s="15" t="s">
+      <c r="G6" s="14" t="s">
         <v>18</v>
       </c>
       <c r="H6" s="7">
@@ -1463,8 +1486,11 @@
       </c>
       <c r="J6" s="2"/>
       <c r="K6" s="2"/>
-    </row>
-    <row r="7" spans="1:11" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+      <c r="L6" s="19" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>144</v>
       </c>
@@ -1483,7 +1509,7 @@
       <c r="F7" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="G7" s="15" t="s">
+      <c r="G7" s="14" t="s">
         <v>19</v>
       </c>
       <c r="H7" s="7">
@@ -1494,8 +1520,11 @@
       </c>
       <c r="J7" s="2"/>
       <c r="K7" s="2"/>
-    </row>
-    <row r="8" spans="1:11" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+      <c r="L7" s="19" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>157</v>
       </c>
@@ -1514,7 +1543,7 @@
       <c r="F8" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="G8" s="15" t="s">
+      <c r="G8" s="14" t="s">
         <v>20</v>
       </c>
       <c r="H8" s="7">
@@ -1525,8 +1554,11 @@
       </c>
       <c r="J8" s="2"/>
       <c r="K8" s="2"/>
-    </row>
-    <row r="9" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L8" s="19" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>153</v>
       </c>
@@ -1545,7 +1577,7 @@
       <c r="F9" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="G9" s="15" t="s">
+      <c r="G9" s="14" t="s">
         <v>21</v>
       </c>
       <c r="H9" s="7">
@@ -1556,8 +1588,11 @@
       </c>
       <c r="J9" s="2"/>
       <c r="K9" s="2"/>
-    </row>
-    <row r="10" spans="1:11" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+      <c r="L9" s="19" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
         <v>164</v>
       </c>
@@ -1576,7 +1611,7 @@
       <c r="F10" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="G10" s="15" t="s">
+      <c r="G10" s="14" t="s">
         <v>22</v>
       </c>
       <c r="H10" s="7">
@@ -1587,8 +1622,11 @@
       </c>
       <c r="J10" s="2"/>
       <c r="K10" s="2"/>
-    </row>
-    <row r="11" spans="1:11" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+      <c r="L10" s="19" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>167</v>
       </c>
@@ -1607,7 +1645,7 @@
       <c r="F11" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="G11" s="15" t="s">
+      <c r="G11" s="14" t="s">
         <v>23</v>
       </c>
       <c r="H11" s="7">
@@ -1618,8 +1656,11 @@
       </c>
       <c r="J11" s="2"/>
       <c r="K11" s="2"/>
-    </row>
-    <row r="12" spans="1:11" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+      <c r="L11" s="19" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>166</v>
       </c>
@@ -1638,7 +1679,7 @@
       <c r="F12" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="G12" s="15" t="s">
+      <c r="G12" s="14" t="s">
         <v>24</v>
       </c>
       <c r="H12" s="7">
@@ -1649,8 +1690,11 @@
       </c>
       <c r="J12" s="2"/>
       <c r="K12" s="2"/>
-    </row>
-    <row r="13" spans="1:11" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+      <c r="L12" s="19" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>163</v>
       </c>
@@ -1669,7 +1713,7 @@
       <c r="F13" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="G13" s="15" t="s">
+      <c r="G13" s="14" t="s">
         <v>25</v>
       </c>
       <c r="H13" s="7">
@@ -1680,8 +1724,11 @@
       </c>
       <c r="J13" s="2"/>
       <c r="K13" s="2"/>
-    </row>
-    <row r="14" spans="1:11" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+      <c r="L13" s="19" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>155</v>
       </c>
@@ -1700,7 +1747,7 @@
       <c r="F14" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="G14" s="14" t="s">
+      <c r="G14" s="13" t="s">
         <v>26</v>
       </c>
       <c r="H14" s="2">
@@ -1711,8 +1758,11 @@
       </c>
       <c r="J14" s="2"/>
       <c r="K14" s="2"/>
-    </row>
-    <row r="15" spans="1:11" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+      <c r="L14" s="19" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A15" s="9" t="s">
         <v>151</v>
       </c>
@@ -1731,7 +1781,7 @@
       <c r="F15" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="G15" s="14" t="s">
+      <c r="G15" s="13" t="s">
         <v>13</v>
       </c>
       <c r="H15" s="2">
@@ -1742,8 +1792,11 @@
       </c>
       <c r="J15" s="2"/>
       <c r="K15" s="2"/>
-    </row>
-    <row r="16" spans="1:11" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+      <c r="L15" s="19" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A16" s="9" t="s">
         <v>149</v>
       </c>
@@ -1762,7 +1815,7 @@
       <c r="F16" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="G16" s="15" t="s">
+      <c r="G16" s="14" t="s">
         <v>27</v>
       </c>
       <c r="H16" s="7">
@@ -1773,8 +1826,11 @@
       </c>
       <c r="J16" s="2"/>
       <c r="K16" s="2"/>
-    </row>
-    <row r="17" spans="1:11" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+      <c r="L16" s="19" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>148</v>
       </c>
@@ -1793,7 +1849,7 @@
       <c r="F17" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="G17" s="15" t="s">
+      <c r="G17" s="14" t="s">
         <v>28</v>
       </c>
       <c r="H17" s="7">
@@ -1804,8 +1860,11 @@
       </c>
       <c r="J17" s="2"/>
       <c r="K17" s="2"/>
-    </row>
-    <row r="18" spans="1:11" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+      <c r="L17" s="19" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
         <v>145</v>
       </c>
@@ -1824,7 +1883,7 @@
       <c r="F18" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="G18" s="15" t="s">
+      <c r="G18" s="14" t="s">
         <v>29</v>
       </c>
       <c r="H18" s="7">
@@ -1835,8 +1894,11 @@
       </c>
       <c r="J18" s="2"/>
       <c r="K18" s="2"/>
-    </row>
-    <row r="19" spans="1:11" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+      <c r="L18" s="19" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>168</v>
       </c>
@@ -1855,7 +1917,7 @@
       <c r="F19" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="G19" s="15" t="s">
+      <c r="G19" s="14" t="s">
         <v>30</v>
       </c>
       <c r="H19" s="7">
@@ -1866,8 +1928,11 @@
       </c>
       <c r="J19" s="2"/>
       <c r="K19" s="2"/>
-    </row>
-    <row r="20" spans="1:11" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+      <c r="L19" s="19" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
         <v>177</v>
       </c>
@@ -1886,7 +1951,7 @@
       <c r="F20" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="G20" s="15" t="s">
+      <c r="G20" s="14" t="s">
         <v>31</v>
       </c>
       <c r="H20" s="7">
@@ -1897,8 +1962,11 @@
       </c>
       <c r="J20" s="2"/>
       <c r="K20" s="2"/>
-    </row>
-    <row r="21" spans="1:11" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L20" s="19" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>183</v>
       </c>
@@ -1917,7 +1985,7 @@
       <c r="F21" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="G21" s="15" t="s">
+      <c r="G21" s="14" t="s">
         <v>32</v>
       </c>
       <c r="H21" s="7">
@@ -1928,8 +1996,11 @@
       </c>
       <c r="J21" s="2"/>
       <c r="K21" s="2"/>
-    </row>
-    <row r="22" spans="1:11" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L21" s="19" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>185</v>
       </c>
@@ -1948,7 +2019,7 @@
       <c r="F22" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="G22" s="15" t="s">
+      <c r="G22" s="14" t="s">
         <v>33</v>
       </c>
       <c r="H22" s="7">
@@ -1959,8 +2030,11 @@
       </c>
       <c r="J22" s="2"/>
       <c r="K22" s="2"/>
-    </row>
-    <row r="23" spans="1:11" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+      <c r="L22" s="19" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>181</v>
       </c>
@@ -1979,7 +2053,7 @@
       <c r="F23" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="G23" s="15" t="s">
+      <c r="G23" s="14" t="s">
         <v>34</v>
       </c>
       <c r="H23" s="7">
@@ -1990,8 +2064,11 @@
       </c>
       <c r="J23" s="2"/>
       <c r="K23" s="2"/>
-    </row>
-    <row r="24" spans="1:11" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+      <c r="L23" s="19" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>176</v>
       </c>
@@ -2010,7 +2087,7 @@
       <c r="F24" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="G24" s="15" t="s">
+      <c r="G24" s="14" t="s">
         <v>35</v>
       </c>
       <c r="H24" s="7">
@@ -2021,8 +2098,11 @@
       </c>
       <c r="J24" s="2"/>
       <c r="K24" s="2"/>
-    </row>
-    <row r="25" spans="1:11" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+      <c r="L24" s="19" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>179</v>
       </c>
@@ -2041,7 +2121,7 @@
       <c r="F25" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="G25" s="15" t="s">
+      <c r="G25" s="14" t="s">
         <v>36</v>
       </c>
       <c r="H25" s="7">
@@ -2052,8 +2132,11 @@
       </c>
       <c r="J25" s="2"/>
       <c r="K25" s="2"/>
-    </row>
-    <row r="26" spans="1:11" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+      <c r="L25" s="19" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>172</v>
       </c>
@@ -2072,7 +2155,7 @@
       <c r="F26" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="G26" s="15" t="s">
+      <c r="G26" s="14" t="s">
         <v>37</v>
       </c>
       <c r="H26" s="7">
@@ -2083,8 +2166,11 @@
       </c>
       <c r="J26" s="2"/>
       <c r="K26" s="2"/>
-    </row>
-    <row r="27" spans="1:11" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+      <c r="L26" s="19" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>174</v>
       </c>
@@ -2103,7 +2189,7 @@
       <c r="F27" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="G27" s="15" t="s">
+      <c r="G27" s="14" t="s">
         <v>38</v>
       </c>
       <c r="H27" s="7">
@@ -2114,8 +2200,11 @@
       </c>
       <c r="J27" s="2"/>
       <c r="K27" s="2"/>
-    </row>
-    <row r="28" spans="1:11" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+      <c r="L27" s="19" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>170</v>
       </c>
@@ -2134,7 +2223,7 @@
       <c r="F28" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="G28" s="15" t="s">
+      <c r="G28" s="14" t="s">
         <v>39</v>
       </c>
       <c r="H28" s="7">
@@ -2145,8 +2234,11 @@
       </c>
       <c r="J28" s="2"/>
       <c r="K28" s="2"/>
-    </row>
-    <row r="29" spans="1:11" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+      <c r="L28" s="19" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>174</v>
       </c>
@@ -2165,7 +2257,7 @@
       <c r="F29" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="G29" s="15" t="s">
+      <c r="G29" s="14" t="s">
         <v>40</v>
       </c>
       <c r="H29" s="7">
@@ -2176,8 +2268,11 @@
       </c>
       <c r="J29" s="2"/>
       <c r="K29" s="2"/>
-    </row>
-    <row r="30" spans="1:11" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+      <c r="L29" s="19" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A30" s="9" t="s">
         <v>186</v>
       </c>
@@ -2196,7 +2291,7 @@
       <c r="F30" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="G30" s="15" t="s">
+      <c r="G30" s="14" t="s">
         <v>41</v>
       </c>
       <c r="H30" s="7">
@@ -2207,8 +2302,11 @@
       </c>
       <c r="J30" s="2"/>
       <c r="K30" s="2"/>
-    </row>
-    <row r="31" spans="1:11" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+      <c r="L30" s="19" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>188</v>
       </c>
@@ -2227,7 +2325,7 @@
       <c r="F31" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="G31" s="15" t="s">
+      <c r="G31" s="14" t="s">
         <v>42</v>
       </c>
       <c r="H31" s="7">
@@ -2238,8 +2336,11 @@
       </c>
       <c r="J31" s="2"/>
       <c r="K31" s="2"/>
-    </row>
-    <row r="32" spans="1:11" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+      <c r="L31" s="19" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>198</v>
       </c>
@@ -2258,7 +2359,7 @@
       <c r="F32" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="G32" s="15" t="s">
+      <c r="G32" s="14" t="s">
         <v>43</v>
       </c>
       <c r="H32" s="7">
@@ -2269,8 +2370,11 @@
       </c>
       <c r="J32" s="2"/>
       <c r="K32" s="2"/>
-    </row>
-    <row r="33" spans="1:11" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+      <c r="L32" s="19" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A33" s="9" t="s">
         <v>190</v>
       </c>
@@ -2289,7 +2393,7 @@
       <c r="F33" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="G33" s="15" t="s">
+      <c r="G33" s="14" t="s">
         <v>44</v>
       </c>
       <c r="H33" s="7">
@@ -2300,8 +2404,11 @@
       </c>
       <c r="J33" s="2"/>
       <c r="K33" s="2"/>
-    </row>
-    <row r="34" spans="1:11" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+      <c r="L33" s="19" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>195</v>
       </c>
@@ -2320,7 +2427,7 @@
       <c r="F34" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="G34" s="15" t="s">
+      <c r="G34" s="14" t="s">
         <v>45</v>
       </c>
       <c r="H34" s="7">
@@ -2331,8 +2438,11 @@
       </c>
       <c r="J34" s="2"/>
       <c r="K34" s="2"/>
-    </row>
-    <row r="35" spans="1:11" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+      <c r="L34" s="19" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
         <v>200</v>
       </c>
@@ -2351,7 +2461,7 @@
       <c r="F35" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="G35" s="15" t="s">
+      <c r="G35" s="14" t="s">
         <v>46</v>
       </c>
       <c r="H35" s="7">
@@ -2362,8 +2472,11 @@
       </c>
       <c r="J35" s="2"/>
       <c r="K35" s="2"/>
-    </row>
-    <row r="36" spans="1:11" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+      <c r="L35" s="19" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A36" s="9" t="s">
         <v>196</v>
       </c>
@@ -2382,7 +2495,7 @@
       <c r="F36" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="G36" s="15" t="s">
+      <c r="G36" s="14" t="s">
         <v>47</v>
       </c>
       <c r="H36" s="7">
@@ -2393,8 +2506,11 @@
       </c>
       <c r="J36" s="2"/>
       <c r="K36" s="2"/>
-    </row>
-    <row r="37" spans="1:11" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+      <c r="L36" s="19" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
         <v>193</v>
       </c>
@@ -2413,7 +2529,7 @@
       <c r="F37" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="G37" s="15" t="s">
+      <c r="G37" s="14" t="s">
         <v>48</v>
       </c>
       <c r="H37" s="7">
@@ -2424,8 +2540,11 @@
       </c>
       <c r="J37" s="2"/>
       <c r="K37" s="2"/>
-    </row>
-    <row r="38" spans="1:11" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+      <c r="L37" s="19" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
         <v>246</v>
       </c>
@@ -2440,7 +2559,7 @@
       <c r="F38" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="G38" s="15" t="s">
+      <c r="G38" s="14" t="s">
         <v>49</v>
       </c>
       <c r="H38" s="7">
@@ -2451,8 +2570,11 @@
       </c>
       <c r="J38" s="2"/>
       <c r="K38" s="2"/>
-    </row>
-    <row r="39" spans="1:11" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+      <c r="L38" s="19" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A39" s="9" t="s">
         <v>202</v>
       </c>
@@ -2471,7 +2593,7 @@
       <c r="F39" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="G39" s="15" t="s">
+      <c r="G39" s="14" t="s">
         <v>51</v>
       </c>
       <c r="H39" s="7">
@@ -2482,8 +2604,11 @@
       </c>
       <c r="J39" s="2"/>
       <c r="K39" s="2"/>
-    </row>
-    <row r="40" spans="1:11" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+      <c r="L39" s="19" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
         <v>211</v>
       </c>
@@ -2502,7 +2627,7 @@
       <c r="F40" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="G40" s="15" t="s">
+      <c r="G40" s="14" t="s">
         <v>52</v>
       </c>
       <c r="H40" s="7">
@@ -2513,8 +2638,11 @@
       </c>
       <c r="J40" s="2"/>
       <c r="K40" s="2"/>
-    </row>
-    <row r="41" spans="1:11" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+      <c r="L40" s="19" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A41" s="9" t="s">
         <v>205</v>
       </c>
@@ -2533,7 +2661,7 @@
       <c r="F41" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="G41" s="15" t="s">
+      <c r="G41" s="14" t="s">
         <v>53</v>
       </c>
       <c r="H41" s="7">
@@ -2544,8 +2672,11 @@
       </c>
       <c r="J41" s="2"/>
       <c r="K41" s="2"/>
-    </row>
-    <row r="42" spans="1:11" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+      <c r="L41" s="19" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
         <v>207</v>
       </c>
@@ -2564,7 +2695,7 @@
       <c r="F42" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="G42" s="15" t="s">
+      <c r="G42" s="14" t="s">
         <v>54</v>
       </c>
       <c r="H42" s="7">
@@ -2575,8 +2706,11 @@
       </c>
       <c r="J42" s="2"/>
       <c r="K42" s="2"/>
-    </row>
-    <row r="43" spans="1:11" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+      <c r="L42" s="19" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A43" s="10" t="s">
         <v>203</v>
       </c>
@@ -2595,7 +2729,7 @@
       <c r="F43" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="G43" s="15" t="s">
+      <c r="G43" s="14" t="s">
         <v>55</v>
       </c>
       <c r="H43" s="7">
@@ -2606,8 +2740,11 @@
       </c>
       <c r="J43" s="2"/>
       <c r="K43" s="2"/>
-    </row>
-    <row r="44" spans="1:11" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+      <c r="L43" s="19" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A44" s="9" t="s">
         <v>209</v>
       </c>
@@ -2626,7 +2763,7 @@
       <c r="F44" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="G44" s="15" t="s">
+      <c r="G44" s="14" t="s">
         <v>56</v>
       </c>
       <c r="H44" s="7">
@@ -2637,8 +2774,11 @@
       </c>
       <c r="J44" s="2"/>
       <c r="K44" s="2"/>
-    </row>
-    <row r="45" spans="1:11" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+      <c r="L44" s="19" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
         <v>213</v>
       </c>
@@ -2657,7 +2797,7 @@
       <c r="F45" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="G45" s="15" t="s">
+      <c r="G45" s="14" t="s">
         <v>57</v>
       </c>
       <c r="H45" s="7">
@@ -2668,8 +2808,11 @@
       </c>
       <c r="J45" s="2"/>
       <c r="K45" s="2"/>
-    </row>
-    <row r="46" spans="1:11" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+      <c r="L45" s="19" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A46" s="9" t="s">
         <v>223</v>
       </c>
@@ -2688,7 +2831,7 @@
       <c r="F46" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="G46" s="15" t="s">
+      <c r="G46" s="14" t="s">
         <v>58</v>
       </c>
       <c r="H46" s="7">
@@ -2699,8 +2842,11 @@
       </c>
       <c r="J46" s="2"/>
       <c r="K46" s="2"/>
-    </row>
-    <row r="47" spans="1:11" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+      <c r="L46" s="19" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A47" s="9" t="s">
         <v>219</v>
       </c>
@@ -2719,7 +2865,7 @@
       <c r="F47" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="G47" s="15" t="s">
+      <c r="G47" s="14" t="s">
         <v>59</v>
       </c>
       <c r="H47" s="7">
@@ -2730,8 +2876,11 @@
       </c>
       <c r="J47" s="2"/>
       <c r="K47" s="2"/>
-    </row>
-    <row r="48" spans="1:11" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+      <c r="L47" s="19" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A48" s="10" t="s">
         <v>214</v>
       </c>
@@ -2750,7 +2899,7 @@
       <c r="F48" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="G48" s="15" t="s">
+      <c r="G48" s="14" t="s">
         <v>60</v>
       </c>
       <c r="H48" s="7">
@@ -2761,8 +2910,11 @@
       </c>
       <c r="J48" s="2"/>
       <c r="K48" s="2"/>
-    </row>
-    <row r="49" spans="1:11" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+      <c r="L48" s="19" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
         <v>216</v>
       </c>
@@ -2781,7 +2933,7 @@
       <c r="F49" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="G49" s="15" t="s">
+      <c r="G49" s="14" t="s">
         <v>61</v>
       </c>
       <c r="H49" s="7">
@@ -2792,8 +2944,11 @@
       </c>
       <c r="J49" s="2"/>
       <c r="K49" s="2"/>
-    </row>
-    <row r="50" spans="1:11" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+      <c r="L49" s="19" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
         <v>228</v>
       </c>
@@ -2812,7 +2967,7 @@
       <c r="F50" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="G50" s="17" t="s">
+      <c r="G50" s="16" t="s">
         <v>63</v>
       </c>
       <c r="H50" s="7">
@@ -2823,8 +2978,11 @@
       </c>
       <c r="J50" s="2"/>
       <c r="K50" s="2"/>
-    </row>
-    <row r="51" spans="1:11" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+      <c r="L50" s="19" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
         <v>224</v>
       </c>
@@ -2843,7 +3001,7 @@
       <c r="F51" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="G51" s="17" t="s">
+      <c r="G51" s="16" t="s">
         <v>62</v>
       </c>
       <c r="H51" s="7">
@@ -2854,8 +3012,11 @@
       </c>
       <c r="J51" s="2"/>
       <c r="K51" s="2"/>
-    </row>
-    <row r="52" spans="1:11" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+      <c r="L51" s="19" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
         <v>218</v>
       </c>
@@ -2874,7 +3035,7 @@
       <c r="F52" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="G52" s="15" t="s">
+      <c r="G52" s="14" t="s">
         <v>64</v>
       </c>
       <c r="H52" s="7">
@@ -2885,8 +3046,11 @@
       </c>
       <c r="J52" s="2"/>
       <c r="K52" s="2"/>
-    </row>
-    <row r="53" spans="1:11" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+      <c r="L52" s="19" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A53" s="9" t="s">
         <v>221</v>
       </c>
@@ -2905,7 +3069,7 @@
       <c r="F53" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="G53" s="15" t="s">
+      <c r="G53" s="14" t="s">
         <v>65</v>
       </c>
       <c r="H53" s="7">
@@ -2916,8 +3080,11 @@
       </c>
       <c r="J53" s="2"/>
       <c r="K53" s="2"/>
-    </row>
-    <row r="54" spans="1:11" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+      <c r="L53" s="19" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
         <v>230</v>
       </c>
@@ -2936,7 +3103,7 @@
       <c r="F54" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="G54" s="15" t="s">
+      <c r="G54" s="14" t="s">
         <v>66</v>
       </c>
       <c r="H54" s="7">
@@ -2947,8 +3114,11 @@
       </c>
       <c r="J54" s="2"/>
       <c r="K54" s="2"/>
-    </row>
-    <row r="55" spans="1:11" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+      <c r="L54" s="19" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A55" s="3" t="s">
         <v>226</v>
       </c>
@@ -2967,7 +3137,7 @@
       <c r="F55" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="G55" s="15" t="s">
+      <c r="G55" s="14" t="s">
         <v>67</v>
       </c>
       <c r="H55" s="7">
@@ -2978,8 +3148,11 @@
       </c>
       <c r="J55" s="2"/>
       <c r="K55" s="2"/>
-    </row>
-    <row r="56" spans="1:11" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+      <c r="L55" s="19" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="56" spans="1:12" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
         <v>244</v>
       </c>
@@ -2998,7 +3171,7 @@
       <c r="F56" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="G56" s="15" t="s">
+      <c r="G56" s="14" t="s">
         <v>68</v>
       </c>
       <c r="H56" s="7">
@@ -3009,8 +3182,11 @@
       </c>
       <c r="J56" s="2"/>
       <c r="K56" s="2"/>
-    </row>
-    <row r="57" spans="1:11" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+      <c r="L56" s="19" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="57" spans="1:12" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
         <v>236</v>
       </c>
@@ -3029,7 +3205,7 @@
       <c r="F57" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="G57" s="15" t="s">
+      <c r="G57" s="14" t="s">
         <v>69</v>
       </c>
       <c r="H57" s="7">
@@ -3040,8 +3216,11 @@
       </c>
       <c r="J57" s="2"/>
       <c r="K57" s="2"/>
-    </row>
-    <row r="58" spans="1:11" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+      <c r="L57" s="19" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="58" spans="1:12" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
         <v>245</v>
       </c>
@@ -3060,7 +3239,7 @@
       <c r="F58" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="G58" s="15" t="s">
+      <c r="G58" s="14" t="s">
         <v>70</v>
       </c>
       <c r="H58" s="7">
@@ -3071,8 +3250,11 @@
       </c>
       <c r="J58" s="2"/>
       <c r="K58" s="2"/>
-    </row>
-    <row r="59" spans="1:11" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+      <c r="L58" s="19" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="59" spans="1:12" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A59" s="10" t="s">
         <v>240</v>
       </c>
@@ -3091,7 +3273,7 @@
       <c r="F59" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="G59" s="15" t="s">
+      <c r="G59" s="14" t="s">
         <v>71</v>
       </c>
       <c r="H59" s="7">
@@ -3102,8 +3284,11 @@
       </c>
       <c r="J59" s="2"/>
       <c r="K59" s="2"/>
-    </row>
-    <row r="60" spans="1:11" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+      <c r="L59" s="19" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="60" spans="1:12" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A60" s="9" t="s">
         <v>238</v>
       </c>
@@ -3122,7 +3307,7 @@
       <c r="F60" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="G60" s="15" t="s">
+      <c r="G60" s="14" t="s">
         <v>72</v>
       </c>
       <c r="H60" s="7">
@@ -3133,8 +3318,11 @@
       </c>
       <c r="J60" s="2"/>
       <c r="K60" s="2"/>
-    </row>
-    <row r="61" spans="1:11" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+      <c r="L60" s="19" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="61" spans="1:12" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
         <v>242</v>
       </c>
@@ -3153,7 +3341,7 @@
       <c r="F61" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="G61" s="15" t="s">
+      <c r="G61" s="14" t="s">
         <v>73</v>
       </c>
       <c r="H61" s="7">
@@ -3164,8 +3352,11 @@
       </c>
       <c r="J61" s="2"/>
       <c r="K61" s="2"/>
-    </row>
-    <row r="62" spans="1:11" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+      <c r="L61" s="19" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="62" spans="1:12" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
         <v>232</v>
       </c>
@@ -3184,7 +3375,7 @@
       <c r="F62" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="G62" s="15" t="s">
+      <c r="G62" s="14" t="s">
         <v>74</v>
       </c>
       <c r="H62" s="7">
@@ -3195,8 +3386,11 @@
       </c>
       <c r="J62" s="2"/>
       <c r="K62" s="2"/>
-    </row>
-    <row r="63" spans="1:11" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+      <c r="L62" s="19" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="63" spans="1:12" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
         <v>233</v>
       </c>
@@ -3215,7 +3409,7 @@
       <c r="F63" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="G63" s="15" t="s">
+      <c r="G63" s="14" t="s">
         <v>75</v>
       </c>
       <c r="H63" s="7">
@@ -3226,8 +3420,11 @@
       </c>
       <c r="J63" s="2"/>
       <c r="K63" s="2"/>
-    </row>
-    <row r="64" spans="1:11" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+      <c r="L63" s="19" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="64" spans="1:12" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
         <v>234</v>
       </c>
@@ -3246,7 +3443,7 @@
       <c r="F64" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="G64" s="15" t="s">
+      <c r="G64" s="14" t="s">
         <v>76</v>
       </c>
       <c r="H64" s="7">
@@ -3257,8 +3454,11 @@
       </c>
       <c r="J64" s="2"/>
       <c r="K64" s="2"/>
-    </row>
-    <row r="65" spans="1:11" s="1" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L64" s="19" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="65" spans="1:12" s="1" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
         <v>233</v>
       </c>
@@ -3277,7 +3477,7 @@
       <c r="F65" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="G65" s="15" t="s">
+      <c r="G65" s="14" t="s">
         <v>77</v>
       </c>
       <c r="H65" s="7">
@@ -3288,190 +3488,179 @@
       </c>
       <c r="J65" s="2"/>
       <c r="K65" s="2"/>
-    </row>
-    <row r="66" spans="1:11" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+      <c r="L65" s="19" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="66" spans="1:12" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A66" s="5"/>
       <c r="B66" s="5"/>
       <c r="C66" s="5"/>
       <c r="D66" s="5"/>
       <c r="E66" s="5"/>
       <c r="F66" s="5"/>
-      <c r="G66" s="13"/>
       <c r="H66" s="5"/>
       <c r="I66" s="5"/>
       <c r="J66" s="5"/>
       <c r="K66" s="5"/>
     </row>
-    <row r="67" spans="1:11" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:12" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A67" s="5"/>
       <c r="B67" s="5"/>
       <c r="C67" s="5"/>
       <c r="D67" s="5"/>
       <c r="E67" s="5"/>
       <c r="F67" s="5"/>
-      <c r="G67" s="13"/>
       <c r="H67" s="5"/>
       <c r="I67" s="5"/>
       <c r="J67" s="5"/>
       <c r="K67" s="5"/>
     </row>
-    <row r="68" spans="1:11" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:12" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A68" s="5"/>
       <c r="B68" s="5"/>
       <c r="C68" s="5"/>
       <c r="D68" s="5"/>
       <c r="E68" s="5"/>
       <c r="F68" s="5"/>
-      <c r="G68" s="13"/>
       <c r="H68" s="5"/>
       <c r="I68" s="5"/>
       <c r="J68" s="5"/>
       <c r="K68" s="5"/>
     </row>
-    <row r="69" spans="1:11" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:12" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A69" s="5"/>
       <c r="B69" s="5"/>
       <c r="C69" s="5"/>
       <c r="D69" s="5"/>
       <c r="E69" s="5"/>
       <c r="F69" s="5"/>
-      <c r="G69" s="13"/>
       <c r="H69" s="5"/>
       <c r="I69" s="5"/>
       <c r="J69" s="5"/>
       <c r="K69" s="5"/>
     </row>
-    <row r="70" spans="1:11" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:12" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A70" s="5"/>
       <c r="B70" s="5"/>
       <c r="C70" s="5"/>
       <c r="D70" s="5"/>
       <c r="E70" s="5"/>
       <c r="F70" s="5"/>
-      <c r="G70" s="13"/>
       <c r="H70" s="5"/>
       <c r="I70" s="5"/>
       <c r="J70" s="5"/>
       <c r="K70" s="5"/>
     </row>
-    <row r="71" spans="1:11" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:12" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A71" s="5"/>
       <c r="B71" s="5"/>
       <c r="C71" s="5"/>
       <c r="D71" s="5"/>
       <c r="E71" s="5"/>
       <c r="F71" s="5"/>
-      <c r="G71" s="13"/>
       <c r="H71" s="5"/>
       <c r="I71" s="5"/>
       <c r="J71" s="5"/>
       <c r="K71" s="5"/>
     </row>
-    <row r="72" spans="1:11" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:12" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A72" s="5"/>
       <c r="B72" s="5"/>
       <c r="C72" s="5"/>
       <c r="D72" s="5"/>
       <c r="E72" s="5"/>
       <c r="F72" s="5"/>
-      <c r="G72" s="13"/>
       <c r="H72" s="5"/>
       <c r="I72" s="5"/>
       <c r="J72" s="5"/>
       <c r="K72" s="5"/>
     </row>
-    <row r="73" spans="1:11" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:12" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A73" s="5"/>
       <c r="B73" s="5"/>
       <c r="C73" s="5"/>
       <c r="D73" s="5"/>
       <c r="E73" s="5"/>
       <c r="F73" s="5"/>
-      <c r="G73" s="13"/>
       <c r="H73" s="5"/>
       <c r="I73" s="5"/>
       <c r="J73" s="5"/>
       <c r="K73" s="5"/>
     </row>
-    <row r="74" spans="1:11" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:12" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A74" s="5"/>
       <c r="B74" s="5"/>
       <c r="C74" s="5"/>
       <c r="D74" s="5"/>
       <c r="E74" s="5"/>
       <c r="F74" s="5"/>
-      <c r="G74" s="13"/>
       <c r="H74" s="5"/>
       <c r="I74" s="5"/>
       <c r="J74" s="5"/>
       <c r="K74" s="5"/>
     </row>
-    <row r="75" spans="1:11" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:12" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A75" s="5"/>
       <c r="B75" s="5"/>
       <c r="C75" s="5"/>
       <c r="D75" s="5"/>
       <c r="E75" s="5"/>
       <c r="F75" s="5"/>
-      <c r="G75" s="13"/>
       <c r="H75" s="5"/>
       <c r="I75" s="5"/>
       <c r="J75" s="5"/>
       <c r="K75" s="5"/>
     </row>
-    <row r="76" spans="1:11" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:12" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A76" s="5"/>
       <c r="B76" s="5"/>
       <c r="C76" s="5"/>
       <c r="D76" s="5"/>
       <c r="E76" s="5"/>
       <c r="F76" s="5"/>
-      <c r="G76" s="13"/>
       <c r="H76" s="5"/>
       <c r="I76" s="5"/>
       <c r="J76" s="5"/>
       <c r="K76" s="5"/>
     </row>
-    <row r="77" spans="1:11" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:12" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A77" s="5"/>
       <c r="B77" s="5"/>
       <c r="C77" s="5"/>
       <c r="D77" s="5"/>
       <c r="E77" s="5"/>
       <c r="F77" s="5"/>
-      <c r="G77" s="13"/>
       <c r="H77" s="5"/>
       <c r="I77" s="5"/>
       <c r="J77" s="5"/>
       <c r="K77" s="5"/>
     </row>
-    <row r="78" spans="1:11" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:12" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A78" s="5"/>
       <c r="B78" s="5"/>
       <c r="C78" s="5"/>
       <c r="D78" s="5"/>
       <c r="E78" s="5"/>
       <c r="F78" s="5"/>
-      <c r="G78" s="13"/>
       <c r="H78" s="5"/>
       <c r="I78" s="5"/>
       <c r="J78" s="5"/>
       <c r="K78" s="5"/>
     </row>
-    <row r="79" spans="1:11" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:12" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A79" s="5"/>
       <c r="B79" s="5"/>
       <c r="C79" s="5"/>
       <c r="D79" s="5"/>
       <c r="E79" s="5"/>
       <c r="F79" s="5"/>
-      <c r="G79" s="13"/>
       <c r="H79" s="5"/>
       <c r="I79" s="5"/>
       <c r="J79" s="5"/>
       <c r="K79" s="5"/>
     </row>
-    <row r="80" spans="1:11" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:12" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A80" s="5"/>
       <c r="B80" s="5"/>
       <c r="C80" s="5"/>
